--- a/laporan_padel_dki_jakarta_2026-09-25.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-25.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.498.000</t>
+          <t>Rp2.399.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.431.985</t>
+          <t>Rp7.949.984</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.928.000</t>
+          <t>Rp3.228.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>64</v>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.325.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>64</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.890.000</t>
+          <t>Rp5.210.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>96</v>
       </c>
       <c r="D47" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp5.237.000</t>
+          <t>Rp5.377.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.455.000</t>
+          <t>Rp1.240.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.168.000</t>
+          <t>Rp4.032.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp8.580.000</t>
+          <t>Rp8.900.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp780.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>112</v>
       </c>
       <c r="D75" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp1.830.000</t>
+          <t>Rp2.370.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>34</v>
       </c>
       <c r="D93" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.235.006</t>
+          <t>Rp15.374.006</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.065.000</t>
+          <t>Rp1.425.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.280.000</t>
+          <t>Rp4.560.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.048.000</t>
+          <t>Rp3.248.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>28</v>
       </c>
       <c r="D37" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp378.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>159</v>
       </c>
       <c r="D38" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp26.250.000</t>
+          <t>Rp26.400.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>90</v>
       </c>
       <c r="D52" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.275.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp15.100.000</t>
+          <t>Rp15.350.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6317,7 +6317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6394,28 +6394,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RacketGo Sunter</t>
+          <t>Gaskan Pendekar Arena</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.155.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rp90.000 - Rp560.000</t>
+          <t>Rp80.000 - Rp2.400.000</t>
         </is>
       </c>
     </row>
@@ -6425,28 +6425,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Olympus Prime Sports Center - Bandengan</t>
+          <t>RacketGo Sunter</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>216</v>
+        <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>153</v>
+        <v>34</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp13.340.000</t>
+          <t>Rp11.155.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp275.000</t>
+          <t>Rp90.000 - Rp560.000</t>
         </is>
       </c>
     </row>
@@ -6456,28 +6456,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Master Padel - Sunter</t>
+          <t>The Royale Padel</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>144</v>
+        <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.350.000</t>
+          <t>Rp1.063.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rp175.000 - Rp350.000</t>
+          <t>Rp50.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -6487,28 +6487,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Anfa Arena Padel</t>
+          <t>Olympus Prime Sports Center - Bandengan</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>54</v>
+        <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp13.340.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rp175.000 - Rp250.000</t>
+          <t>Rp150.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -6518,28 +6518,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MXL Ground</t>
+          <t>Master Padel - Sunter</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp8.206.000</t>
+          <t>Rp3.625.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp250.000</t>
+          <t>Rp175.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -6549,28 +6549,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ultradome Padel Tennis Lounge</t>
+          <t>Anfa Arena Padel</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>216</v>
+        <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>153</v>
+        <v>46</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp16.009.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp280.000</t>
+          <t>Rp175.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -6580,28 +6580,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The 40/0 Club</t>
+          <t>MXL Ground</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp8.206.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp50.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -6611,28 +6611,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>El Patio Padel - Pluit</t>
+          <t>Kinesis Padel</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.178.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rp188.000 - Rp558.000</t>
+          <t>Rp150.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -6642,28 +6642,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Batavia Sports Club</t>
+          <t>Ultradome Padel Tennis Lounge</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>144</v>
+        <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp7.790.000</t>
+          <t>Rp16.009.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp275.000</t>
+          <t>Rp50.000 - Rp280.000</t>
         </is>
       </c>
     </row>
@@ -6673,28 +6673,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vibora Padel &amp; Pickleball Club Kelapa Gading</t>
+          <t>The 40/0 Club</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.275.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp250.000</t>
+          <t>Rp200.000</t>
         </is>
       </c>
     </row>
@@ -6704,28 +6704,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Northside Padel Court &amp; Mahjong</t>
+          <t>El Patio Padel - Pluit</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.878.000</t>
+          <t>Rp3.178.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rp88.000 - Rp325.000</t>
+          <t>Rp188.000 - Rp558.000</t>
         </is>
       </c>
     </row>
@@ -6735,28 +6735,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mega Padel</t>
+          <t>Batavia Sports Club</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp7.790.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp150.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -6766,28 +6766,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Padel Hive Pluit</t>
+          <t>The Palm Padel</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.679.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp538.000</t>
+          <t>Rp75.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -6797,28 +6797,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Atlantic Padel Indonesia</t>
+          <t>Vibora Padel &amp; Pickleball Club Kelapa Gading</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp6.375.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp100.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -6828,28 +6828,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Urban Racquet Club</t>
+          <t>Northside Padel Court &amp; Mahjong</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D17" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp23.200.000</t>
+          <t>Rp6.910.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp600.000</t>
+          <t>Rp88.000 - Rp325.000</t>
         </is>
       </c>
     </row>
@@ -6859,28 +6859,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vamos! Padel House - Sunter</t>
+          <t>Mega Padel</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp10.175.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp350.000</t>
+          <t>Rp150.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -6890,28 +6890,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DeWarehouse Padel ( DWP ) - Sunter</t>
+          <t>Padel Hive Pluit</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp11.096.000</t>
+          <t>Rp4.679.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rp81.000 - Rp299.000</t>
+          <t>Rp99.000 - Rp538.000</t>
         </is>
       </c>
     </row>
@@ -6921,28 +6921,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VIP Padel MK</t>
+          <t>Atlantic Padel Indonesia</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>Rp1.188.000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Rp99.000</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Rp99.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -6952,28 +6952,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>My Club House - Padel</t>
+          <t>Urban Racquet Club</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp6.296.000</t>
+          <t>Rp23.200.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rp199.000 - Rp275.000</t>
+          <t>Rp200.000 - Rp600.000</t>
         </is>
       </c>
     </row>
@@ -6983,28 +6983,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MSC Padel Sunter</t>
+          <t>Vamos! Padel House - Sunter</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.435.000</t>
+          <t>Rp10.175.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp175.000</t>
+          <t>Rp200.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -7014,28 +7014,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Heliix Padel</t>
+          <t>DeWarehouse Padel ( DWP ) - Sunter</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp8.650.000</t>
+          <t>Rp9.576.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp250.000</t>
+          <t>Rp81.000 - Rp299.000</t>
         </is>
       </c>
     </row>
@@ -7045,28 +7045,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Garuda Padel Club</t>
+          <t>VIP Padel MK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.070.000</t>
+          <t>Rp99.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp345.000</t>
+          <t>Rp99.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -7076,28 +7076,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Padel Commons</t>
+          <t>My Club House - Padel</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp6.296.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp285.000</t>
+          <t>Rp199.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -7107,28 +7107,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bandeja Padel Arena</t>
+          <t>MSC Padel Sunter</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.530.000</t>
+          <t>Rp1.525.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rp195.000 - Rp245.000</t>
+          <t>Rp50.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7138,28 +7138,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fivestar Signature Club</t>
+          <t>Heliix Padel</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>187</v>
+        <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp14.975.000</t>
+          <t>Rp8.650.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp500.000</t>
+          <t>Rp150.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -7169,28 +7169,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rivera Padel Pluit</t>
+          <t>Garuda Padel Club</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp5.812.000</t>
+          <t>Rp2.070.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp348.000</t>
+          <t>Rp150.000 - Rp345.000</t>
         </is>
       </c>
     </row>
@@ -7200,28 +7200,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Happy Padel Place</t>
+          <t>Cometa Padel VIP Lounge</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D29" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp6.470.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rp149.000 - Rp285.000</t>
+          <t>Rp140.000 - Rp860.000</t>
         </is>
       </c>
     </row>
@@ -7231,28 +7231,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>X3 Padel</t>
+          <t>Padel Go Blast</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D30" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp6.470.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp200.000</t>
+          <t>Rp145.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -7262,28 +7262,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Club House Padel - Pantai Mutiara Pluit</t>
+          <t>Padel Commons</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp864.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rp188.000 - Rp288.000</t>
+          <t>Rp125.000 - Rp285.000</t>
         </is>
       </c>
     </row>
@@ -7293,28 +7293,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Staple Social Club</t>
+          <t>Bandeja Padel Arena</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp5.530.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rp175.000</t>
+          <t>Rp195.000 - Rp245.000</t>
         </is>
       </c>
     </row>
@@ -7324,28 +7324,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pluit Padel Parq (PPP)</t>
+          <t>Fivestar Signature Club</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp25.500.000</t>
+          <t>Rp15.175.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp425.000</t>
+          <t>Rp75.000 - Rp500.000</t>
         </is>
       </c>
     </row>
@@ -7355,28 +7355,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Genesis Padel Club</t>
+          <t>Rivera Padel Pluit</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.150.000</t>
+          <t>Rp5.812.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp275.000</t>
+          <t>Rp100.000 - Rp348.000</t>
         </is>
       </c>
     </row>
@@ -7386,28 +7386,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Padel Guru JIS</t>
+          <t>Happy Padel Place</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp11.520.000</t>
+          <t>Rp298.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rp180.000 - Rp300.000</t>
+          <t>Rp149.000 - Rp285.000</t>
         </is>
       </c>
     </row>
@@ -7417,28 +7417,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gading Mas Racquet Club</t>
+          <t>X3 Padel</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp12.140.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp275.000</t>
+          <t>Rp125.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -7448,28 +7448,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>YOLO Sports &amp; Lifestyle Pluit</t>
+          <t>The Club House Padel - Pantai Mutiara Pluit</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="D37" t="n">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp31.000.000</t>
+          <t>Rp864.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp700.000</t>
+          <t>Rp188.000 - Rp288.000</t>
         </is>
       </c>
     </row>
@@ -7479,28 +7479,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Raquette Temple Sunter</t>
+          <t>Staple Social Club</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp7.080.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp400.000</t>
+          <t>Rp175.000</t>
         </is>
       </c>
     </row>
@@ -7510,28 +7510,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Foreground  Racquet Simulator - Sunter</t>
+          <t>Pluit Padel Parq (PPP)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp25.500.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rp275.000</t>
+          <t>Rp200.000 - Rp425.000</t>
         </is>
       </c>
     </row>
@@ -7541,28 +7541,338 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>Nord Social Club</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>104</v>
+      </c>
+      <c r="D40" t="n">
+        <v>92</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>11.5%</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Rp4.600.000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Rp350.000 - Rp599.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Genesis Padel Club</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>80</v>
+      </c>
+      <c r="D41" t="n">
+        <v>60</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Rp4.150.000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Rp150.000 - Rp275.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Padel Guru JIS</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>56</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rp11.520.000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Rp180.000 - Rp300.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Gading Mas Racquet Club</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>112</v>
+      </c>
+      <c r="D43" t="n">
+        <v>59</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>47.3%</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rp12.265.000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Rp125.000 - Rp275.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>YOLO Sports &amp; Lifestyle Pluit</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>174</v>
+      </c>
+      <c r="D44" t="n">
+        <v>114</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>34.5%</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rp31.000.000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Rp150.000 - Rp700.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Foreground Racquet Simulator - Pluit</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>84</v>
+      </c>
+      <c r="D45" t="n">
+        <v>78</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>7.1%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rp1.310.000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Rp205.000 - Rp225.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>The Raquette Temple Sunter</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>36</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rp7.080.000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rp250.000 - Rp400.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Foreground  Racquet Simulator - Sunter</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>108</v>
+      </c>
+      <c r="D47" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rp2.200.000</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Rp275.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Let's Go Padel Sunter</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C48" t="n">
         <v>98</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D48" t="n">
         <v>84</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>14.3%</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Rp3.620.000</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Rp150.000 - Rp350.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Padre Padel Kelapa Gading</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>120</v>
+      </c>
+      <c r="D49" t="n">
+        <v>92</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>23.3%</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Rp4.900.000</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Rp125.000 - Rp175.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>wePADL at Meridian Sports &amp; Wellness (MSW) PIK</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>48</v>
+      </c>
+      <c r="D50" t="n">
+        <v>44</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rp900.000</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Rp200.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -7661,16 +7971,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.320.000</t>
+          <t>Rp11.780.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7723,16 +8033,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.100.000</t>
+          <t>Rp8.350.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8033,16 +8343,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8653,16 +8963,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.225.000</t>
+          <t>Rp1.990.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8870,16 +9180,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.592.000</t>
+          <t>Rp1.990.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8901,16 +9211,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-25.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-25.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.399.000</t>
+          <t>Rp2.498.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp13.860.000</t>
+          <t>Rp15.150.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.289.000</t>
+          <t>Rp2.380.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.310.000</t>
+          <t>Rp9.810.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.475.000</t>
+          <t>Rp1.775.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.140.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.816.000</t>
+          <t>Rp15.091.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>68</v>
       </c>
       <c r="D25" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp398.000</t>
+          <t>Rp696.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp752.000</t>
+          <t>Rp877.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.396.000</t>
+          <t>Rp3.592.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.890.000</t>
+          <t>Rp2.670.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>60</v>
       </c>
       <c r="D44" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.099.000</t>
+          <t>Rp1.699.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp260.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>18</v>
       </c>
       <c r="D55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp847.000</t>
+          <t>Rp996.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp2.495.000</t>
+          <t>Rp1.895.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>54</v>
       </c>
       <c r="D57" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp590.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.825.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp149.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>112</v>
       </c>
       <c r="D60" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp3.091.000</t>
+          <t>Rp3.191.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp3.187.000</t>
+          <t>Rp3.985.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>32</v>
       </c>
       <c r="D67" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.810.000</t>
+          <t>Rp1.885.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>120</v>
       </c>
       <c r="D76" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp6.240.000</t>
+          <t>Rp7.020.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>80</v>
       </c>
       <c r="D79" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>108</v>
       </c>
       <c r="D84" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>80</v>
       </c>
       <c r="D86" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp2.239.000</t>
+          <t>Rp2.438.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>138</v>
       </c>
       <c r="D87" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp3.940.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>68</v>
       </c>
       <c r="D96" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.540.000</t>
+          <t>Rp4.020.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp648.000</t>
+          <t>Rp729.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.374.006</t>
+          <t>Rp15.944.006</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp5.834.000</t>
+          <t>Rp7.234.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp8.280.000</t>
+          <t>Rp8.430.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.097.000</t>
+          <t>Rp3.272.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp10.935.000</t>
+          <t>Rp12.555.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp99.000</t>
+          <t>Rp59.000 - Rp99.000</t>
         </is>
       </c>
     </row>
@@ -4160,16 +4160,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.745.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp3.837.000</t>
+          <t>Rp4.136.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp5.510.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>28</v>
       </c>
       <c r="D37" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp378.000</t>
+          <t>Rp567.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>159</v>
       </c>
       <c r="D38" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp26.400.000</t>
+          <t>Rp24.300.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp2.376.000</t>
+          <t>Rp3.372.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp7.950.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp9.775.000</t>
+          <t>Rp8.525.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>128</v>
       </c>
       <c r="D58" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp381.000</t>
+          <t>Rp452.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>51</v>
       </c>
       <c r="D60" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5400,21 +5400,21 @@
         <v>45</v>
       </c>
       <c r="D63" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp300.000 - Rp475.000</t>
+          <t>Rp250.000 - Rp475.000</t>
         </is>
       </c>
     </row>
@@ -5431,16 +5431,16 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.240.000</t>
+          <t>Rp2.765.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp7.812.000</t>
+          <t>Rp8.406.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp12.600.000</t>
+          <t>Rp15.900.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.575.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp420.000</t>
+          <t>Rp480.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp15.350.000</t>
+          <t>Rp16.100.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp45.150.000</t>
+          <t>Rp45.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.940.000</t>
+          <t>Rp7.120.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.763.000</t>
+          <t>Rp3.268.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.430.000</t>
+          <t>Rp3.810.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp6.960.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.460.000</t>
+          <t>Rp14.140.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>71</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.340.000</t>
+          <t>Rp13.435.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.625.000</t>
+          <t>Rp1.525.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>108</v>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.206.000</t>
+          <t>Rp8.806.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>56</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp16.009.000</t>
+          <t>Rp16.569.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.178.000</t>
+          <t>Rp3.736.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp9.576.000</t>
+          <t>Rp8.056.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.296.000</t>
+          <t>Rp6.846.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>68</v>
       </c>
       <c r="D28" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.070.000</t>
+          <t>Rp2.760.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp2.360.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp5.530.000</t>
+          <t>Rp5.775.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp15.175.000</t>
+          <t>Rp16.125.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp583.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp25.500.000</t>
+          <t>Rp27.750.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.150.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp31.000.000</t>
+          <t>Rp33.000.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>120</v>
       </c>
       <c r="D49" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7940,16 +7940,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.860.000</t>
+          <t>Rp2.170.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.780.000</t>
+          <t>Rp12.820.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.060.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp8.745.000</t>
+          <t>Rp8.955.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.751.000</t>
+          <t>Rp6.201.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp3.875.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp16.540.000</t>
+          <t>Rp17.800.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp955.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp1.975.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.626.000</t>
+          <t>Rp2.676.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.670.000</t>
+          <t>Rp4.970.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp713.000</t>
+          <t>Rp1.220.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-25.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-25.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.498.000</t>
+          <t>Rp3.948.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp15.150.000</t>
+          <t>Rp15.650.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.380.000</t>
+          <t>Rp2.479.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp7.590.000</t>
+          <t>Rp8.140.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.949.984</t>
+          <t>Rp8.805.983</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.810.000</t>
+          <t>Rp9.310.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp15.594.500</t>
+          <t>Rp16.753.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp15.091.000</t>
+          <t>Rp15.391.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>64</v>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>68</v>
       </c>
       <c r="D25" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp696.000</t>
+          <t>Rp795.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>68</v>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.350.000</t>
+          <t>Rp4.100.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>64</v>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.210.000</t>
+          <t>Rp5.630.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.493.000</t>
+          <t>Rp1.883.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>51</v>
       </c>
       <c r="D41" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.640.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>180</v>
       </c>
       <c r="D42" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp10.150.000</t>
+          <t>Rp9.100.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>180</v>
       </c>
       <c r="D43" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>54</v>
       </c>
       <c r="D46" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.080.000</t>
+          <t>Rp280.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>96</v>
       </c>
       <c r="D47" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp5.377.000</t>
+          <t>Rp5.674.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.895.000</t>
+          <t>Rp1.695.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>54</v>
       </c>
       <c r="D57" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp590.000</t>
+          <t>Rp1.085.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp149.000</t>
+          <t>Rp645.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>112</v>
       </c>
       <c r="D60" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp3.191.000</t>
+          <t>Rp3.390.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>32</v>
       </c>
       <c r="D65" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp5.475.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp3.985.000</t>
+          <t>Rp3.586.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.844.000</t>
+          <t>Rp4.449.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.960.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.475.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp3.555.000</t>
+          <t>Rp4.075.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>112</v>
       </c>
       <c r="D75" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.370.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>120</v>
       </c>
       <c r="D76" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp7.020.000</t>
+          <t>Rp7.410.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>108</v>
       </c>
       <c r="D77" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>96</v>
       </c>
       <c r="D78" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>80</v>
       </c>
       <c r="D79" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>14</v>
       </c>
       <c r="D82" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>138</v>
       </c>
       <c r="D87" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp4.625.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>90</v>
       </c>
       <c r="D88" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>68</v>
       </c>
       <c r="D96" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp4.020.000</t>
+          <t>Rp3.795.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp729.000</t>
+          <t>Rp810.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.944.006</t>
+          <t>Rp16.243.006</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp7.234.000</t>
+          <t>Rp8.712.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp8.430.000</t>
+          <t>Rp7.030.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.146.000</t>
+          <t>Rp2.321.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.965.000</t>
+          <t>Rp7.545.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.272.000</t>
+          <t>Rp3.797.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.560.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp12.555.000</t>
+          <t>Rp12.960.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>53</v>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp11.900.000</t>
+          <t>Rp12.300.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.136.000</t>
+          <t>Rp4.734.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>180</v>
       </c>
       <c r="D29" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp20.940.000</t>
+          <t>Rp21.440.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.248.000</t>
+          <t>Rp3.648.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>32</v>
       </c>
       <c r="D33" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>90</v>
       </c>
       <c r="D34" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp5.875.000</t>
+          <t>Rp5.375.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>159</v>
       </c>
       <c r="D38" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp24.300.000</t>
+          <t>Rp24.150.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp7.396.000</t>
+          <t>Rp6.496.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp1.725.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp3.372.000</t>
+          <t>Rp2.580.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp9.150.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.950.000</t>
+          <t>Rp8.650.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>72</v>
       </c>
       <c r="D56" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp2.240.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp8.525.000</t>
+          <t>Rp9.185.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp452.000</t>
+          <t>Rp806.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>51</v>
       </c>
       <c r="D60" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.765.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp8.406.000</t>
+          <t>Rp8.703.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp8.925.000</t>
+          <t>Rp8.225.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp45.400.000</t>
+          <t>Rp47.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.120.000</t>
+          <t>Rp7.970.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.810.000</t>
+          <t>Rp5.090.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp14.140.000</t>
+          <t>Rp11.220.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.063.000</t>
+          <t>Rp1.132.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.525.000</t>
+          <t>Rp2.225.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.736.000</t>
+          <t>Rp4.294.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp7.790.000</t>
+          <t>Rp8.340.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.375.000</t>
+          <t>Rp6.475.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp23.200.000</t>
+          <t>Rp23.400.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp8.056.000</t>
+          <t>Rp7.159.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>70</v>
       </c>
       <c r="D30" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp6.470.000</t>
+          <t>Rp4.820.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.360.000</t>
+          <t>Rp3.215.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp5.775.000</t>
+          <t>Rp6.265.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp16.125.000</t>
+          <t>Rp17.700.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp5.812.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp27.750.000</t>
+          <t>Rp28.450.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>104</v>
       </c>
       <c r="D40" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>98</v>
       </c>
       <c r="D48" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.620.000</t>
+          <t>Rp4.640.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>120</v>
       </c>
       <c r="D49" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp6.475.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.820.000</t>
+          <t>Rp12.945.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.350.000</t>
+          <t>Rp9.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.887.000</t>
+          <t>Rp3.588.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.785.000</t>
+          <t>Rp2.415.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp8.955.000</t>
+          <t>Rp9.765.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.875.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp3.880.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.330.000</t>
+          <t>Rp1.520.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.395.000</t>
+          <t>Rp1.710.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.735.000</t>
+          <t>Rp4.980.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.745.000</t>
+          <t>Rp5.315.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.390.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.150.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.087.000</t>
+          <t>Rp4.577.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.990.000</t>
+          <t>Rp2.780.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.975.000</t>
+          <t>Rp2.160.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.970.000</t>
+          <t>Rp4.170.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.220.000</t>
+          <t>Rp1.896.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>72</v>
       </c>
       <c r="D41" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.275.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-25.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-25.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.760.000</t>
+          <t>Rp1.840.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.753.500</t>
+          <t>Rp17.239.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>68</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.286.000</t>
+          <t>Rp2.385.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>85</v>
       </c>
       <c r="D32" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.314.000</t>
+          <t>Rp1.514.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.720.000</t>
+          <t>Rp5.345.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>180</v>
       </c>
       <c r="D43" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.140.000</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.449.000</t>
+          <t>Rp4.549.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>108</v>
       </c>
       <c r="D77" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>96</v>
       </c>
       <c r="D78" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.525.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>36</v>
       </c>
       <c r="D92" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp714.000</t>
+          <t>Rp813.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.030.000</t>
+          <t>Rp7.380.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.475.000</t>
+          <t>Rp6.675.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp9.185.000</t>
+          <t>Rp9.460.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp47.400.000</t>
+          <t>Rp47.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.970.000</t>
+          <t>Rp7.470.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.090.000</t>
+          <t>Rp5.280.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.960.000</t>
+          <t>Rp7.235.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.220.000</t>
+          <t>Rp11.300.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>71</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.132.000</t>
+          <t>Rp1.707.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp23.400.000</t>
+          <t>Rp24.400.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.525.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp8.650.000</t>
+          <t>Rp8.900.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp6.265.000</t>
+          <t>Rp6.460.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7340,12 +7340,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp17.700.000</t>
+          <t>Rp17.500.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp500.000</t>
+          <t>Rp50.000 - Rp500.000</t>
         </is>
       </c>
     </row>
@@ -7424,16 +7424,16 @@
         <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>36</v>
       </c>
       <c r="D46" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp7.080.000</t>
+          <t>Rp7.730.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.945.000</t>
+          <t>Rp13.070.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.415.000</t>
+          <t>Rp2.565.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.201.000</t>
+          <t>Rp6.426.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.125.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.520.000</t>
+          <t>Rp1.690.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp2.160.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.980.000</t>
+          <t>Rp5.160.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.577.000</t>
+          <t>Rp4.087.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.955.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.990.000</t>
+          <t>Rp2.189.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-25.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-25.xlsx
@@ -3881,16 +3881,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.675.000</t>
+          <t>Rp6.875.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.470.000</t>
+          <t>Rp7.720.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp2.385.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
